--- a/Web crawling/Review/Review_category.xlsx
+++ b/Web crawling/Review/Review_category.xlsx
@@ -66570,12 +66570,12 @@
     <row r="2363">
       <c r="A2363" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2363" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2363" s="1" t="inlineStr">
@@ -66584,7 +66584,7 @@
         </is>
       </c>
       <c r="D2363" s="1" t="n">
-        <v>924</v>
+        <v>1592</v>
       </c>
       <c r="E2363" s="1" t="inlineStr">
         <is>
@@ -66592,74 +66592,74 @@
         </is>
       </c>
       <c r="F2363" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2364">
       <c r="A2364" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2364" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2364" s="1" t="inlineStr">
         <is>
-          <t>인테리어가 멋져요</t>
+          <t>커피가 맛있어요</t>
         </is>
       </c>
       <c r="D2364" s="1" t="n">
-        <v>701</v>
+        <v>777</v>
       </c>
       <c r="E2364" s="1" t="inlineStr">
         <is>
-          <t>인테리어</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2364" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2365">
       <c r="A2365" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2365" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2365" s="1" t="inlineStr">
         <is>
-          <t>커피가 맛있어요</t>
+          <t>친절해요</t>
         </is>
       </c>
       <c r="D2365" s="1" t="n">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="E2365" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F2365" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2366">
       <c r="A2366" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2366" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2366" s="1" t="inlineStr">
@@ -66668,7 +66668,7 @@
         </is>
       </c>
       <c r="D2366" s="1" t="n">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="E2366" s="1" t="inlineStr">
         <is>
@@ -66676,111 +66676,111 @@
         </is>
       </c>
       <c r="F2366" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2367">
       <c r="A2367" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2367" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2367" s="1" t="inlineStr">
         <is>
-          <t>친절해요</t>
+          <t>인테리어가 멋져요</t>
         </is>
       </c>
       <c r="D2367" s="1" t="n">
-        <v>500</v>
+        <v>628</v>
       </c>
       <c r="E2367" s="1" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>인테리어</t>
         </is>
       </c>
       <c r="F2367" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2368">
       <c r="A2368" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2368" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2368" s="1" t="inlineStr">
         <is>
-          <t>특별한 메뉴가 있어요</t>
+          <t>대화하기 좋아요</t>
         </is>
       </c>
       <c r="D2368" s="1" t="n">
-        <v>456</v>
+        <v>481</v>
       </c>
       <c r="E2368" s="1" t="inlineStr">
         <is>
-          <t>메뉴</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2368" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2369">
       <c r="A2369" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2369" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2369" s="1" t="inlineStr">
         <is>
-          <t>사진이 잘 나와요</t>
+          <t>특별한 메뉴가 있어요</t>
         </is>
       </c>
       <c r="D2369" s="1" t="n">
-        <v>350</v>
+        <v>429</v>
       </c>
       <c r="E2369" s="1" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>메뉴</t>
         </is>
       </c>
       <c r="F2369" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2370">
       <c r="A2370" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2370" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2370" s="1" t="inlineStr">
         <is>
-          <t>대화하기 좋아요</t>
+          <t>아늑해요</t>
         </is>
       </c>
       <c r="D2370" s="1" t="n">
-        <v>350</v>
+        <v>425</v>
       </c>
       <c r="E2370" s="1" t="inlineStr">
         <is>
@@ -66788,130 +66788,130 @@
         </is>
       </c>
       <c r="F2370" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2371">
       <c r="A2371" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2371" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2371" s="1" t="inlineStr">
         <is>
-          <t>매장이 청결해요</t>
+          <t>사진이 잘 나와요</t>
         </is>
       </c>
       <c r="D2371" s="1" t="n">
-        <v>344</v>
+        <v>304</v>
       </c>
       <c r="E2371" s="1" t="inlineStr">
         <is>
-          <t>청결도</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="F2371" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2372">
       <c r="A2372" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2372" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2372" s="1" t="inlineStr">
         <is>
-          <t>음식이 맛있어요</t>
+          <t>매장이 청결해요</t>
         </is>
       </c>
       <c r="D2372" s="1" t="n">
-        <v>178</v>
+        <v>249</v>
       </c>
       <c r="E2372" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>청결도</t>
         </is>
       </c>
       <c r="F2372" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2373">
       <c r="A2373" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2373" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2373" s="1" t="inlineStr">
         <is>
-          <t>뷰가 좋아요</t>
+          <t>빵이 맛있어요</t>
         </is>
       </c>
       <c r="D2373" s="1" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="E2373" s="1" t="inlineStr">
         <is>
-          <t>전망</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2373" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2374">
       <c r="A2374" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2374" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2374" s="1" t="inlineStr">
         <is>
-          <t>집중하기 좋아요</t>
+          <t>음식이 맛있어요</t>
         </is>
       </c>
       <c r="D2374" s="1" t="n">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E2374" s="1" t="inlineStr">
         <is>
-          <t>편의</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2374" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2375">
       <c r="A2375" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2375" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2375" s="1" t="inlineStr">
@@ -66920,7 +66920,7 @@
         </is>
       </c>
       <c r="D2375" s="1" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E2375" s="1" t="inlineStr">
         <is>
@@ -66928,191 +66928,191 @@
         </is>
       </c>
       <c r="F2375" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2376">
       <c r="A2376" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2376" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2376" s="1" t="inlineStr">
         <is>
-          <t>좌석이 편해요</t>
+          <t>음악이 좋아요</t>
         </is>
       </c>
       <c r="D2376" s="1" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="E2376" s="1" t="inlineStr">
         <is>
-          <t>편의</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2376" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2377">
       <c r="A2377" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2377" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2377" s="1" t="inlineStr">
         <is>
-          <t>주차하기 편해요</t>
+          <t>차분한 분위기예요</t>
         </is>
       </c>
       <c r="D2377" s="1" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="E2377" s="1" t="inlineStr">
         <is>
-          <t>편의</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2377" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2378">
       <c r="A2378" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2378" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2378" s="1" t="inlineStr">
         <is>
-          <t>차분한 분위기예요</t>
+          <t>가성비가 좋아요</t>
         </is>
       </c>
       <c r="D2378" s="1" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E2378" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>가격</t>
         </is>
       </c>
       <c r="F2378" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2379">
       <c r="A2379" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2379" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2379" s="1" t="inlineStr">
         <is>
-          <t>아늑해요</t>
+          <t>메뉴 구성이 알차요</t>
         </is>
       </c>
       <c r="D2379" s="1" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="E2379" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>메뉴</t>
         </is>
       </c>
       <c r="F2379" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2380">
       <c r="A2380" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2380" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2380" s="1" t="inlineStr">
         <is>
-          <t>음악이 좋아요</t>
+          <t>종류가 다양해요</t>
         </is>
       </c>
       <c r="D2380" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2380" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>메뉴</t>
         </is>
       </c>
       <c r="F2380" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2381">
       <c r="A2381" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2381" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2381" s="1" t="inlineStr">
         <is>
-          <t>컨셉이 독특해요</t>
+          <t>양이 많아요</t>
         </is>
       </c>
       <c r="D2381" s="1" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E2381" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>음식량</t>
         </is>
       </c>
       <c r="F2381" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2382">
       <c r="A2382" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2382" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2382" s="1" t="inlineStr">
         <is>
-          <t>건강한 맛이에요</t>
+          <t>좌석이 편해요</t>
         </is>
       </c>
       <c r="D2382" s="1" t="n">
@@ -67120,339 +67120,339 @@
       </c>
       <c r="E2382" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>편의</t>
         </is>
       </c>
       <c r="F2382" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2383">
       <c r="A2383" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2383" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2383" s="1" t="inlineStr">
         <is>
-          <t>가성비가 좋아요</t>
+          <t>재료가 신선해요</t>
         </is>
       </c>
       <c r="D2383" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2383" s="1" t="inlineStr">
         <is>
-          <t>가격</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2383" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2384">
       <c r="A2384" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2384" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2384" s="1" t="inlineStr">
         <is>
-          <t>매장이 넓어요</t>
+          <t>비싼 만큼 가치있어요</t>
         </is>
       </c>
       <c r="D2384" s="1" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2384" s="1" t="inlineStr">
         <is>
-          <t>공간</t>
+          <t>가격</t>
         </is>
       </c>
       <c r="F2384" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2385">
       <c r="A2385" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2385" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2385" s="1" t="inlineStr">
         <is>
-          <t>차가 맛있어요</t>
+          <t>컨셉이 독특해요</t>
         </is>
       </c>
       <c r="D2385" s="1" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E2385" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2385" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2386">
       <c r="A2386" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2386" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2386" s="1" t="inlineStr">
         <is>
-          <t>메뉴 구성이 알차요</t>
+          <t>뷰가 좋아요</t>
         </is>
       </c>
       <c r="D2386" s="1" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E2386" s="1" t="inlineStr">
         <is>
-          <t>메뉴</t>
+          <t>전망</t>
         </is>
       </c>
       <c r="F2386" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2387">
       <c r="A2387" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2387" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2387" s="1" t="inlineStr">
         <is>
-          <t>반려동물과 가기 좋아요</t>
+          <t>혼밥하기 좋아요</t>
         </is>
       </c>
       <c r="D2387" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2387" s="1" t="inlineStr">
         <is>
-          <t>편의</t>
+          <t>목적</t>
         </is>
       </c>
       <c r="F2387" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2388">
       <c r="A2388" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2388" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2388" s="1" t="inlineStr">
         <is>
-          <t>종류가 다양해요</t>
+          <t>집중하기 좋아요</t>
         </is>
       </c>
       <c r="D2388" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E2388" s="1" t="inlineStr">
         <is>
-          <t>메뉴</t>
+          <t>편의</t>
         </is>
       </c>
       <c r="F2388" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2389">
       <c r="A2389" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2389" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2389" s="1" t="inlineStr">
         <is>
-          <t>빵이 맛있어요</t>
+          <t>특별한 날 가기 좋아요</t>
         </is>
       </c>
       <c r="D2389" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2389" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>목적</t>
         </is>
       </c>
       <c r="F2389" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2390">
       <c r="A2390" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2390" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2390" s="1" t="inlineStr">
         <is>
-          <t>혼술하기 좋아요</t>
+          <t>차가 맛있어요</t>
         </is>
       </c>
       <c r="D2390" s="1" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E2390" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2390" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2391">
       <c r="A2391" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2391" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2391" s="1" t="inlineStr">
         <is>
-          <t>재료가 신선해요</t>
+          <t>음식이 빨리 나와요</t>
         </is>
       </c>
       <c r="D2391" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2391" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F2391" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2392">
       <c r="A2392" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2392" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2392" s="1" t="inlineStr">
         <is>
-          <t>술이 다양해요</t>
+          <t>아이와 가기 좋아요</t>
         </is>
       </c>
       <c r="D2392" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2392" s="1" t="inlineStr">
         <is>
-          <t>메뉴</t>
+          <t>목적</t>
         </is>
       </c>
       <c r="F2392" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2393">
       <c r="A2393" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2393" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2393" s="1" t="inlineStr">
         <is>
-          <t>음식이 빨리 나와요</t>
+          <t>야외공간이 멋져요</t>
         </is>
       </c>
       <c r="D2393" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2393" s="1" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>전망</t>
         </is>
       </c>
       <c r="F2393" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2394">
       <c r="A2394" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2394" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2394" s="1" t="inlineStr">
         <is>
-          <t>단체모임 하기 좋아요</t>
+          <t>오래 머무르기 좋아요</t>
         </is>
       </c>
       <c r="D2394" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2394" s="1" t="inlineStr">
         <is>
@@ -67460,51 +67460,51 @@
         </is>
       </c>
       <c r="F2394" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2395">
       <c r="A2395" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2395" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2395" s="1" t="inlineStr">
         <is>
-          <t>야외공간이 멋져요</t>
+          <t>건강한 맛이에요</t>
         </is>
       </c>
       <c r="D2395" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2395" s="1" t="inlineStr">
         <is>
-          <t>전망</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2395" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2396">
       <c r="A2396" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B2396" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>폴리스팬케이크 연남점</t>
         </is>
       </c>
       <c r="C2396" s="1" t="inlineStr">
         <is>
-          <t>코스요리가 알차요</t>
+          <t>단체모임 하기 좋아요</t>
         </is>
       </c>
       <c r="D2396" s="1" t="n">
@@ -67512,227 +67512,227 @@
       </c>
       <c r="E2396" s="1" t="inlineStr">
         <is>
-          <t>메뉴</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2396" s="1" t="n">
-        <v>1486</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="2397">
       <c r="A2397" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2397" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2397" s="1" t="inlineStr">
         <is>
-          <t>양이 많아요</t>
+          <t>인테리어가 멋져요</t>
         </is>
       </c>
       <c r="D2397" s="1" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="E2397" s="1" t="inlineStr">
         <is>
-          <t>음식량</t>
+          <t>인테리어</t>
         </is>
       </c>
       <c r="F2397" s="1" t="n">
-        <v>1486</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2398">
       <c r="A2398" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2398" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2398" s="1" t="inlineStr">
         <is>
-          <t>비싼 만큼 가치있어요</t>
+          <t>친절해요</t>
         </is>
       </c>
       <c r="D2398" s="1" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="E2398" s="1" t="inlineStr">
         <is>
-          <t>가격</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F2398" s="1" t="n">
-        <v>1486</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2399">
       <c r="A2399" s="1" t="inlineStr">
         <is>
-          <t>S001</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2399" s="1" t="inlineStr">
         <is>
-          <t>롱베케이션</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2399" s="1" t="inlineStr">
         <is>
-          <t>오래 머무르기 좋아요</t>
+          <t>매장이 청결해요</t>
         </is>
       </c>
       <c r="D2399" s="1" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E2399" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>청결도</t>
         </is>
       </c>
       <c r="F2399" s="1" t="n">
-        <v>1486</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2400">
       <c r="A2400" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2400" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2400" s="1" t="inlineStr">
         <is>
-          <t>디저트가 맛있어요</t>
+          <t>대화하기 좋아요</t>
         </is>
       </c>
       <c r="D2400" s="1" t="n">
-        <v>1592</v>
+        <v>20</v>
       </c>
       <c r="E2400" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2400" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2401">
       <c r="A2401" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2401" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2401" s="1" t="inlineStr">
         <is>
-          <t>커피가 맛있어요</t>
+          <t>집중하기 좋아요</t>
         </is>
       </c>
       <c r="D2401" s="1" t="n">
-        <v>777</v>
+        <v>17</v>
       </c>
       <c r="E2401" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>편의</t>
         </is>
       </c>
       <c r="F2401" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2402">
       <c r="A2402" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2402" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2402" s="1" t="inlineStr">
         <is>
-          <t>친절해요</t>
+          <t>아늑해요</t>
         </is>
       </c>
       <c r="D2402" s="1" t="n">
-        <v>652</v>
+        <v>14</v>
       </c>
       <c r="E2402" s="1" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2402" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2403">
       <c r="A2403" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2403" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2403" s="1" t="inlineStr">
         <is>
-          <t>음료가 맛있어요</t>
+          <t>좌석이 편해요</t>
         </is>
       </c>
       <c r="D2403" s="1" t="n">
-        <v>636</v>
+        <v>11</v>
       </c>
       <c r="E2403" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>편의</t>
         </is>
       </c>
       <c r="F2403" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2404">
       <c r="A2404" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2404" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2404" s="1" t="inlineStr">
         <is>
-          <t>인테리어가 멋져요</t>
+          <t>룸이 잘 되어있어요</t>
         </is>
       </c>
       <c r="D2404" s="1" t="n">
-        <v>628</v>
+        <v>9</v>
       </c>
       <c r="E2404" s="1" t="inlineStr">
         <is>
@@ -67740,195 +67740,195 @@
         </is>
       </c>
       <c r="F2404" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2405">
       <c r="A2405" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2405" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2405" s="1" t="inlineStr">
         <is>
-          <t>대화하기 좋아요</t>
+          <t>매장이 넓어요</t>
         </is>
       </c>
       <c r="D2405" s="1" t="n">
-        <v>481</v>
+        <v>9</v>
       </c>
       <c r="E2405" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>공간</t>
         </is>
       </c>
       <c r="F2405" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2406">
       <c r="A2406" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2406" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2406" s="1" t="inlineStr">
         <is>
-          <t>특별한 메뉴가 있어요</t>
+          <t>사진이 잘 나와요</t>
         </is>
       </c>
       <c r="D2406" s="1" t="n">
-        <v>429</v>
+        <v>8</v>
       </c>
       <c r="E2406" s="1" t="inlineStr">
         <is>
-          <t>메뉴</t>
+          <t>사진</t>
         </is>
       </c>
       <c r="F2406" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2407">
       <c r="A2407" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2407" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2407" s="1" t="inlineStr">
         <is>
-          <t>아늑해요</t>
+          <t>음료가 맛있어요</t>
         </is>
       </c>
       <c r="D2407" s="1" t="n">
-        <v>425</v>
+        <v>7</v>
       </c>
       <c r="E2407" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2407" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2408">
       <c r="A2408" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2408" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2408" s="1" t="inlineStr">
         <is>
-          <t>사진이 잘 나와요</t>
+          <t>가성비가 좋아요</t>
         </is>
       </c>
       <c r="D2408" s="1" t="n">
-        <v>304</v>
+        <v>7</v>
       </c>
       <c r="E2408" s="1" t="inlineStr">
         <is>
-          <t>사진</t>
+          <t>가격</t>
         </is>
       </c>
       <c r="F2408" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2409">
       <c r="A2409" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2409" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2409" s="1" t="inlineStr">
         <is>
-          <t>매장이 청결해요</t>
+          <t>컨셉이 독특해요</t>
         </is>
       </c>
       <c r="D2409" s="1" t="n">
-        <v>249</v>
+        <v>6</v>
       </c>
       <c r="E2409" s="1" t="inlineStr">
         <is>
-          <t>청결도</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2409" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2410">
       <c r="A2410" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2410" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2410" s="1" t="inlineStr">
         <is>
-          <t>빵이 맛있어요</t>
+          <t>특별한 메뉴가 있어요</t>
         </is>
       </c>
       <c r="D2410" s="1" t="n">
-        <v>150</v>
+        <v>5</v>
       </c>
       <c r="E2410" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>메뉴</t>
         </is>
       </c>
       <c r="F2410" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2411">
       <c r="A2411" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2411" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2411" s="1" t="inlineStr">
         <is>
-          <t>음식이 맛있어요</t>
+          <t>커피가 맛있어요</t>
         </is>
       </c>
       <c r="D2411" s="1" t="n">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="E2411" s="1" t="inlineStr">
         <is>
@@ -67936,55 +67936,55 @@
         </is>
       </c>
       <c r="F2411" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2412">
       <c r="A2412" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2412" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2412" s="1" t="inlineStr">
         <is>
-          <t>화장실이 깨끗해요</t>
+          <t>아이와 가기 좋아요</t>
         </is>
       </c>
       <c r="D2412" s="1" t="n">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="E2412" s="1" t="inlineStr">
         <is>
-          <t>청결도</t>
+          <t>목적</t>
         </is>
       </c>
       <c r="F2412" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2413">
       <c r="A2413" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2413" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2413" s="1" t="inlineStr">
         <is>
-          <t>음악이 좋아요</t>
+          <t>오래 머무르기 좋아요</t>
         </is>
       </c>
       <c r="D2413" s="1" t="n">
-        <v>51</v>
+        <v>4</v>
       </c>
       <c r="E2413" s="1" t="inlineStr">
         <is>
@@ -67992,102 +67992,102 @@
         </is>
       </c>
       <c r="F2413" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2414">
       <c r="A2414" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2414" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2414" s="1" t="inlineStr">
         <is>
-          <t>차분한 분위기예요</t>
+          <t>화장실이 깨끗해요</t>
         </is>
       </c>
       <c r="D2414" s="1" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="E2414" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>청결도</t>
         </is>
       </c>
       <c r="F2414" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2415">
       <c r="A2415" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2415" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2415" s="1" t="inlineStr">
         <is>
-          <t>가성비가 좋아요</t>
+          <t>차분한 분위기예요</t>
         </is>
       </c>
       <c r="D2415" s="1" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="E2415" s="1" t="inlineStr">
         <is>
-          <t>가격</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2415" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2416">
       <c r="A2416" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2416" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2416" s="1" t="inlineStr">
         <is>
-          <t>메뉴 구성이 알차요</t>
+          <t>디저트가 맛있어요</t>
         </is>
       </c>
       <c r="D2416" s="1" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="E2416" s="1" t="inlineStr">
         <is>
-          <t>메뉴</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2416" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2417">
       <c r="A2417" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2417" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2417" s="1" t="inlineStr">
@@ -68096,7 +68096,7 @@
         </is>
       </c>
       <c r="D2417" s="1" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="E2417" s="1" t="inlineStr">
         <is>
@@ -68104,139 +68104,139 @@
         </is>
       </c>
       <c r="F2417" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2418">
       <c r="A2418" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2418" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2418" s="1" t="inlineStr">
         <is>
-          <t>양이 많아요</t>
+          <t>음식이 맛있어요</t>
         </is>
       </c>
       <c r="D2418" s="1" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="E2418" s="1" t="inlineStr">
         <is>
-          <t>음식량</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2418" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2419">
       <c r="A2419" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2419" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2419" s="1" t="inlineStr">
         <is>
-          <t>좌석이 편해요</t>
+          <t>선물하기 좋아요</t>
         </is>
       </c>
       <c r="D2419" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E2419" s="1" t="inlineStr">
         <is>
-          <t>편의</t>
+          <t>목적</t>
         </is>
       </c>
       <c r="F2419" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2420">
       <c r="A2420" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2420" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2420" s="1" t="inlineStr">
         <is>
-          <t>재료가 신선해요</t>
+          <t>음악이 좋아요</t>
         </is>
       </c>
       <c r="D2420" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E2420" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2420" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2421">
       <c r="A2421" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2421" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2421" s="1" t="inlineStr">
         <is>
-          <t>비싼 만큼 가치있어요</t>
+          <t>기본 안주가 좋아요</t>
         </is>
       </c>
       <c r="D2421" s="1" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="E2421" s="1" t="inlineStr">
         <is>
-          <t>가격</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2421" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2422">
       <c r="A2422" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2422" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2422" s="1" t="inlineStr">
         <is>
-          <t>컨셉이 독특해요</t>
+          <t>단체모임 하기 좋아요</t>
         </is>
       </c>
       <c r="D2422" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2422" s="1" t="inlineStr">
         <is>
@@ -68244,18 +68244,18 @@
         </is>
       </c>
       <c r="F2422" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2423">
       <c r="A2423" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2423" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2423" s="1" t="inlineStr">
@@ -68264,7 +68264,7 @@
         </is>
       </c>
       <c r="D2423" s="1" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E2423" s="1" t="inlineStr">
         <is>
@@ -68272,135 +68272,135 @@
         </is>
       </c>
       <c r="F2423" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2424">
       <c r="A2424" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2424" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2424" s="1" t="inlineStr">
         <is>
-          <t>혼밥하기 좋아요</t>
+          <t>빵이 맛있어요</t>
         </is>
       </c>
       <c r="D2424" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2424" s="1" t="inlineStr">
         <is>
-          <t>목적</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2424" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2425">
       <c r="A2425" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2425" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2425" s="1" t="inlineStr">
         <is>
-          <t>집중하기 좋아요</t>
+          <t>코스요리가 알차요</t>
         </is>
       </c>
       <c r="D2425" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E2425" s="1" t="inlineStr">
         <is>
-          <t>편의</t>
+          <t>메뉴</t>
         </is>
       </c>
       <c r="F2425" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2426">
       <c r="A2426" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2426" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2426" s="1" t="inlineStr">
         <is>
-          <t>특별한 날 가기 좋아요</t>
+          <t>주문제작을 잘해줘요</t>
         </is>
       </c>
       <c r="D2426" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2426" s="1" t="inlineStr">
         <is>
-          <t>목적</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F2426" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2427">
       <c r="A2427" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2427" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2427" s="1" t="inlineStr">
         <is>
-          <t>차가 맛있어요</t>
+          <t>혼술하기 좋아요</t>
         </is>
       </c>
       <c r="D2427" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2427" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2427" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2428">
       <c r="A2428" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2428" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2428" s="1" t="inlineStr">
         <is>
-          <t>음식이 빨리 나와요</t>
+          <t>혼밥하기 좋아요</t>
         </is>
       </c>
       <c r="D2428" s="1" t="n">
@@ -68408,27 +68408,27 @@
       </c>
       <c r="E2428" s="1" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>목적</t>
         </is>
       </c>
       <c r="F2428" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2429">
       <c r="A2429" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2429" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2429" s="1" t="inlineStr">
         <is>
-          <t>아이와 가기 좋아요</t>
+          <t>음식이 빨리 나와요</t>
         </is>
       </c>
       <c r="D2429" s="1" t="n">
@@ -68436,27 +68436,27 @@
       </c>
       <c r="E2429" s="1" t="inlineStr">
         <is>
-          <t>목적</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F2429" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2430">
       <c r="A2430" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2430" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2430" s="1" t="inlineStr">
         <is>
-          <t>야외공간이 멋져요</t>
+          <t>재료가 신선해요</t>
         </is>
       </c>
       <c r="D2430" s="1" t="n">
@@ -68464,27 +68464,27 @@
       </c>
       <c r="E2430" s="1" t="inlineStr">
         <is>
-          <t>전망</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2430" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2431">
       <c r="A2431" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2431" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2431" s="1" t="inlineStr">
         <is>
-          <t>오래 머무르기 좋아요</t>
+          <t>양이 많아요</t>
         </is>
       </c>
       <c r="D2431" s="1" t="n">
@@ -68492,27 +68492,27 @@
       </c>
       <c r="E2431" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>음식량</t>
         </is>
       </c>
       <c r="F2431" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2432">
       <c r="A2432" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2432" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2432" s="1" t="inlineStr">
         <is>
-          <t>건강한 맛이에요</t>
+          <t>메뉴 구성이 알차요</t>
         </is>
       </c>
       <c r="D2432" s="1" t="n">
@@ -68520,27 +68520,27 @@
       </c>
       <c r="E2432" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>메뉴</t>
         </is>
       </c>
       <c r="F2432" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2433">
       <c r="A2433" s="1" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S005</t>
         </is>
       </c>
       <c r="B2433" s="1" t="inlineStr">
         <is>
-          <t>폴리스팬케이크 연남점</t>
+          <t>킬링타임오티티카페 홍대점</t>
         </is>
       </c>
       <c r="C2433" s="1" t="inlineStr">
         <is>
-          <t>단체모임 하기 좋아요</t>
+          <t>야외공간이 멋져요</t>
         </is>
       </c>
       <c r="D2433" s="1" t="n">
@@ -68548,11 +68548,11 @@
       </c>
       <c r="E2433" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>전망</t>
         </is>
       </c>
       <c r="F2433" s="1" t="n">
-        <v>1616</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2434">
@@ -68568,15 +68568,15 @@
       </c>
       <c r="C2434" s="1" t="inlineStr">
         <is>
-          <t>인테리어가 멋져요</t>
+          <t>포장이 깔끔해요</t>
         </is>
       </c>
       <c r="D2434" s="1" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="E2434" s="1" t="inlineStr">
         <is>
-          <t>인테리어</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F2434" s="1" t="n">
@@ -68596,15 +68596,15 @@
       </c>
       <c r="C2435" s="1" t="inlineStr">
         <is>
-          <t>친절해요</t>
+          <t>파티하기 좋아요</t>
         </is>
       </c>
       <c r="D2435" s="1" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="E2435" s="1" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>목적</t>
         </is>
       </c>
       <c r="F2435" s="1" t="n">
@@ -68624,15 +68624,15 @@
       </c>
       <c r="C2436" s="1" t="inlineStr">
         <is>
-          <t>매장이 청결해요</t>
+          <t>비싼 만큼 가치있어요</t>
         </is>
       </c>
       <c r="D2436" s="1" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="E2436" s="1" t="inlineStr">
         <is>
-          <t>청결도</t>
+          <t>가격</t>
         </is>
       </c>
       <c r="F2436" s="1" t="n">
@@ -68642,180 +68642,180 @@
     <row r="2437">
       <c r="A2437" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2437" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2437" s="1" t="inlineStr">
         <is>
-          <t>대화하기 좋아요</t>
+          <t>디저트가 맛있어요</t>
         </is>
       </c>
       <c r="D2437" s="1" t="n">
-        <v>20</v>
+        <v>924</v>
       </c>
       <c r="E2437" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2437" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2438">
       <c r="A2438" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2438" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2438" s="1" t="inlineStr">
         <is>
-          <t>집중하기 좋아요</t>
+          <t>인테리어가 멋져요</t>
         </is>
       </c>
       <c r="D2438" s="1" t="n">
-        <v>17</v>
+        <v>701</v>
       </c>
       <c r="E2438" s="1" t="inlineStr">
         <is>
-          <t>편의</t>
+          <t>인테리어</t>
         </is>
       </c>
       <c r="F2438" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2439">
       <c r="A2439" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2439" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2439" s="1" t="inlineStr">
         <is>
-          <t>아늑해요</t>
+          <t>커피가 맛있어요</t>
         </is>
       </c>
       <c r="D2439" s="1" t="n">
-        <v>14</v>
+        <v>651</v>
       </c>
       <c r="E2439" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2439" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2440">
       <c r="A2440" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2440" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2440" s="1" t="inlineStr">
         <is>
-          <t>좌석이 편해요</t>
+          <t>음료가 맛있어요</t>
         </is>
       </c>
       <c r="D2440" s="1" t="n">
-        <v>11</v>
+        <v>639</v>
       </c>
       <c r="E2440" s="1" t="inlineStr">
         <is>
-          <t>편의</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2440" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2441">
       <c r="A2441" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2441" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2441" s="1" t="inlineStr">
         <is>
-          <t>룸이 잘 되어있어요</t>
+          <t>친절해요</t>
         </is>
       </c>
       <c r="D2441" s="1" t="n">
-        <v>9</v>
+        <v>500</v>
       </c>
       <c r="E2441" s="1" t="inlineStr">
         <is>
-          <t>인테리어</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F2441" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2442">
       <c r="A2442" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2442" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2442" s="1" t="inlineStr">
         <is>
-          <t>매장이 넓어요</t>
+          <t>특별한 메뉴가 있어요</t>
         </is>
       </c>
       <c r="D2442" s="1" t="n">
-        <v>9</v>
+        <v>456</v>
       </c>
       <c r="E2442" s="1" t="inlineStr">
         <is>
-          <t>공간</t>
+          <t>메뉴</t>
         </is>
       </c>
       <c r="F2442" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2443">
       <c r="A2443" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2443" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2443" s="1" t="inlineStr">
@@ -68824,7 +68824,7 @@
         </is>
       </c>
       <c r="D2443" s="1" t="n">
-        <v>8</v>
+        <v>350</v>
       </c>
       <c r="E2443" s="1" t="inlineStr">
         <is>
@@ -68832,242 +68832,242 @@
         </is>
       </c>
       <c r="F2443" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2444">
       <c r="A2444" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2444" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2444" s="1" t="inlineStr">
         <is>
-          <t>음료가 맛있어요</t>
+          <t>대화하기 좋아요</t>
         </is>
       </c>
       <c r="D2444" s="1" t="n">
-        <v>7</v>
+        <v>350</v>
       </c>
       <c r="E2444" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2444" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2445">
       <c r="A2445" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2445" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2445" s="1" t="inlineStr">
         <is>
-          <t>가성비가 좋아요</t>
+          <t>매장이 청결해요</t>
         </is>
       </c>
       <c r="D2445" s="1" t="n">
-        <v>7</v>
+        <v>344</v>
       </c>
       <c r="E2445" s="1" t="inlineStr">
         <is>
-          <t>가격</t>
+          <t>청결도</t>
         </is>
       </c>
       <c r="F2445" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2446">
       <c r="A2446" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2446" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2446" s="1" t="inlineStr">
         <is>
-          <t>컨셉이 독특해요</t>
+          <t>음식이 맛있어요</t>
         </is>
       </c>
       <c r="D2446" s="1" t="n">
-        <v>6</v>
+        <v>178</v>
       </c>
       <c r="E2446" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2446" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2447">
       <c r="A2447" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2447" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2447" s="1" t="inlineStr">
         <is>
-          <t>특별한 메뉴가 있어요</t>
+          <t>뷰가 좋아요</t>
         </is>
       </c>
       <c r="D2447" s="1" t="n">
-        <v>5</v>
+        <v>145</v>
       </c>
       <c r="E2447" s="1" t="inlineStr">
         <is>
-          <t>메뉴</t>
+          <t>전망</t>
         </is>
       </c>
       <c r="F2447" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2448">
       <c r="A2448" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2448" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2448" s="1" t="inlineStr">
         <is>
-          <t>커피가 맛있어요</t>
+          <t>집중하기 좋아요</t>
         </is>
       </c>
       <c r="D2448" s="1" t="n">
-        <v>4</v>
+        <v>119</v>
       </c>
       <c r="E2448" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>편의</t>
         </is>
       </c>
       <c r="F2448" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2449">
       <c r="A2449" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2449" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2449" s="1" t="inlineStr">
         <is>
-          <t>아이와 가기 좋아요</t>
+          <t>화장실이 깨끗해요</t>
         </is>
       </c>
       <c r="D2449" s="1" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="E2449" s="1" t="inlineStr">
         <is>
-          <t>목적</t>
+          <t>청결도</t>
         </is>
       </c>
       <c r="F2449" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2450">
       <c r="A2450" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2450" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2450" s="1" t="inlineStr">
         <is>
-          <t>오래 머무르기 좋아요</t>
+          <t>좌석이 편해요</t>
         </is>
       </c>
       <c r="D2450" s="1" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E2450" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>편의</t>
         </is>
       </c>
       <c r="F2450" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2451">
       <c r="A2451" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2451" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2451" s="1" t="inlineStr">
         <is>
-          <t>화장실이 깨끗해요</t>
+          <t>주차하기 편해요</t>
         </is>
       </c>
       <c r="D2451" s="1" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="E2451" s="1" t="inlineStr">
         <is>
-          <t>청결도</t>
+          <t>편의</t>
         </is>
       </c>
       <c r="F2451" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2452">
       <c r="A2452" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2452" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2452" s="1" t="inlineStr">
@@ -69076,7 +69076,7 @@
         </is>
       </c>
       <c r="D2452" s="1" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="E2452" s="1" t="inlineStr">
         <is>
@@ -69084,279 +69084,279 @@
         </is>
       </c>
       <c r="F2452" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2453">
       <c r="A2453" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2453" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2453" s="1" t="inlineStr">
         <is>
-          <t>디저트가 맛있어요</t>
+          <t>아늑해요</t>
         </is>
       </c>
       <c r="D2453" s="1" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="E2453" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2453" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2454">
       <c r="A2454" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2454" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2454" s="1" t="inlineStr">
         <is>
-          <t>종류가 다양해요</t>
+          <t>음악이 좋아요</t>
         </is>
       </c>
       <c r="D2454" s="1" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E2454" s="1" t="inlineStr">
         <is>
-          <t>메뉴</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2454" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2455">
       <c r="A2455" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2455" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2455" s="1" t="inlineStr">
         <is>
-          <t>음식이 맛있어요</t>
+          <t>컨셉이 독특해요</t>
         </is>
       </c>
       <c r="D2455" s="1" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E2455" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2455" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2456">
       <c r="A2456" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2456" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2456" s="1" t="inlineStr">
         <is>
-          <t>선물하기 좋아요</t>
+          <t>건강한 맛이에요</t>
         </is>
       </c>
       <c r="D2456" s="1" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="E2456" s="1" t="inlineStr">
         <is>
-          <t>목적</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2456" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2457">
       <c r="A2457" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2457" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2457" s="1" t="inlineStr">
         <is>
-          <t>음악이 좋아요</t>
+          <t>가성비가 좋아요</t>
         </is>
       </c>
       <c r="D2457" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E2457" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>가격</t>
         </is>
       </c>
       <c r="F2457" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2458">
       <c r="A2458" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2458" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2458" s="1" t="inlineStr">
         <is>
-          <t>기본 안주가 좋아요</t>
+          <t>매장이 넓어요</t>
         </is>
       </c>
       <c r="D2458" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E2458" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>공간</t>
         </is>
       </c>
       <c r="F2458" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2459">
       <c r="A2459" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2459" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2459" s="1" t="inlineStr">
         <is>
-          <t>단체모임 하기 좋아요</t>
+          <t>차가 맛있어요</t>
         </is>
       </c>
       <c r="D2459" s="1" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E2459" s="1" t="inlineStr">
         <is>
-          <t>분위기</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2459" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2460">
       <c r="A2460" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2460" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2460" s="1" t="inlineStr">
         <is>
-          <t>뷰가 좋아요</t>
+          <t>메뉴 구성이 알차요</t>
         </is>
       </c>
       <c r="D2460" s="1" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E2460" s="1" t="inlineStr">
         <is>
-          <t>전망</t>
+          <t>메뉴</t>
         </is>
       </c>
       <c r="F2460" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2461">
       <c r="A2461" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2461" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2461" s="1" t="inlineStr">
         <is>
-          <t>빵이 맛있어요</t>
+          <t>반려동물과 가기 좋아요</t>
         </is>
       </c>
       <c r="D2461" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2461" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>편의</t>
         </is>
       </c>
       <c r="F2461" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2462">
       <c r="A2462" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2462" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2462" s="1" t="inlineStr">
         <is>
-          <t>코스요리가 알차요</t>
+          <t>종류가 다양해요</t>
         </is>
       </c>
       <c r="D2462" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E2462" s="1" t="inlineStr">
         <is>
@@ -69364,46 +69364,46 @@
         </is>
       </c>
       <c r="F2462" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2463">
       <c r="A2463" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2463" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2463" s="1" t="inlineStr">
         <is>
-          <t>주문제작을 잘해줘요</t>
+          <t>빵이 맛있어요</t>
         </is>
       </c>
       <c r="D2463" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2463" s="1" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2463" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2464">
       <c r="A2464" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2464" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2464" s="1" t="inlineStr">
@@ -69412,7 +69412,7 @@
         </is>
       </c>
       <c r="D2464" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2464" s="1" t="inlineStr">
         <is>
@@ -69420,163 +69420,163 @@
         </is>
       </c>
       <c r="F2464" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2465">
       <c r="A2465" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2465" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2465" s="1" t="inlineStr">
         <is>
-          <t>혼밥하기 좋아요</t>
+          <t>재료가 신선해요</t>
         </is>
       </c>
       <c r="D2465" s="1" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E2465" s="1" t="inlineStr">
         <is>
-          <t>목적</t>
+          <t>맛</t>
         </is>
       </c>
       <c r="F2465" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2466">
       <c r="A2466" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2466" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2466" s="1" t="inlineStr">
         <is>
-          <t>음식이 빨리 나와요</t>
+          <t>술이 다양해요</t>
         </is>
       </c>
       <c r="D2466" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2466" s="1" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>메뉴</t>
         </is>
       </c>
       <c r="F2466" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2467">
       <c r="A2467" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2467" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2467" s="1" t="inlineStr">
         <is>
-          <t>재료가 신선해요</t>
+          <t>음식이 빨리 나와요</t>
         </is>
       </c>
       <c r="D2467" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2467" s="1" t="inlineStr">
         <is>
-          <t>맛</t>
+          <t>서비스</t>
         </is>
       </c>
       <c r="F2467" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2468">
       <c r="A2468" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2468" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2468" s="1" t="inlineStr">
         <is>
-          <t>양이 많아요</t>
+          <t>단체모임 하기 좋아요</t>
         </is>
       </c>
       <c r="D2468" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2468" s="1" t="inlineStr">
         <is>
-          <t>음식량</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2468" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2469">
       <c r="A2469" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2469" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2469" s="1" t="inlineStr">
         <is>
-          <t>메뉴 구성이 알차요</t>
+          <t>야외공간이 멋져요</t>
         </is>
       </c>
       <c r="D2469" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2469" s="1" t="inlineStr">
         <is>
-          <t>메뉴</t>
+          <t>전망</t>
         </is>
       </c>
       <c r="F2469" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2470">
       <c r="A2470" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2470" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2470" s="1" t="inlineStr">
         <is>
-          <t>야외공간이 멋져요</t>
+          <t>코스요리가 알차요</t>
         </is>
       </c>
       <c r="D2470" s="1" t="n">
@@ -69584,27 +69584,27 @@
       </c>
       <c r="E2470" s="1" t="inlineStr">
         <is>
-          <t>전망</t>
+          <t>메뉴</t>
         </is>
       </c>
       <c r="F2470" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2471">
       <c r="A2471" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2471" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2471" s="1" t="inlineStr">
         <is>
-          <t>포장이 깔끔해요</t>
+          <t>양이 많아요</t>
         </is>
       </c>
       <c r="D2471" s="1" t="n">
@@ -69612,27 +69612,27 @@
       </c>
       <c r="E2471" s="1" t="inlineStr">
         <is>
-          <t>서비스</t>
+          <t>음식량</t>
         </is>
       </c>
       <c r="F2471" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2472">
       <c r="A2472" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2472" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2472" s="1" t="inlineStr">
         <is>
-          <t>파티하기 좋아요</t>
+          <t>비싼 만큼 가치있어요</t>
         </is>
       </c>
       <c r="D2472" s="1" t="n">
@@ -69640,27 +69640,27 @@
       </c>
       <c r="E2472" s="1" t="inlineStr">
         <is>
-          <t>목적</t>
+          <t>가격</t>
         </is>
       </c>
       <c r="F2472" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="2473">
       <c r="A2473" s="1" t="inlineStr">
         <is>
-          <t>S005</t>
+          <t>S001</t>
         </is>
       </c>
       <c r="B2473" s="1" t="inlineStr">
         <is>
-          <t>킬링타임오티티카페 홍대점</t>
+          <t>롱베케이션</t>
         </is>
       </c>
       <c r="C2473" s="1" t="inlineStr">
         <is>
-          <t>비싼 만큼 가치있어요</t>
+          <t>오래 머무르기 좋아요</t>
         </is>
       </c>
       <c r="D2473" s="1" t="n">
@@ -69668,11 +69668,11 @@
       </c>
       <c r="E2473" s="1" t="inlineStr">
         <is>
-          <t>가격</t>
+          <t>분위기</t>
         </is>
       </c>
       <c r="F2473" s="1" t="n">
-        <v>64</v>
+        <v>1486</v>
       </c>
     </row>
   </sheetData>
